--- a/artfynd/A 10553-2024 artfynd.xlsx
+++ b/artfynd/A 10553-2024 artfynd.xlsx
@@ -4680,10 +4680,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119596070</v>
+        <v>119606595</v>
       </c>
       <c r="B39" t="n">
-        <v>91884</v>
+        <v>90712</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4692,25 +4692,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406104</v>
+        <v>406313</v>
       </c>
       <c r="R39" t="n">
-        <v>6853128</v>
+        <v>6852914</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119606595</v>
+        <v>119605452</v>
       </c>
       <c r="B40" t="n">
-        <v>90712</v>
+        <v>86412</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>3690</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406313</v>
+        <v>406109</v>
       </c>
       <c r="R40" t="n">
-        <v>6852914</v>
+        <v>6853016</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119605452</v>
+        <v>119596070</v>
       </c>
       <c r="B41" t="n">
-        <v>86412</v>
+        <v>91884</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3690</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406109</v>
+        <v>406104</v>
       </c>
       <c r="R41" t="n">
-        <v>6853016</v>
+        <v>6853128</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6006,7 +6006,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119595839</v>
+        <v>119606560</v>
       </c>
       <c r="B52" t="n">
         <v>91840</v>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406032</v>
+        <v>406316</v>
       </c>
       <c r="R52" t="n">
-        <v>6853036</v>
+        <v>6852927</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119606560</v>
+        <v>119606304</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6124,21 +6124,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406316</v>
+        <v>406281</v>
       </c>
       <c r="R53" t="n">
-        <v>6852927</v>
+        <v>6852896</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,10 +6210,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119606304</v>
+        <v>119605062</v>
       </c>
       <c r="B54" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6226,21 +6226,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406281</v>
+        <v>406129</v>
       </c>
       <c r="R54" t="n">
-        <v>6852896</v>
+        <v>6853142</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119605062</v>
+        <v>119595839</v>
       </c>
       <c r="B55" t="n">
         <v>91840</v>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406129</v>
+        <v>406032</v>
       </c>
       <c r="R55" t="n">
-        <v>6853142</v>
+        <v>6853036</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119606057</v>
+        <v>119607335</v>
       </c>
       <c r="B60" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6834,25 +6834,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406112</v>
+        <v>406239</v>
       </c>
       <c r="R60" t="n">
-        <v>6852975</v>
+        <v>6853060</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119607335</v>
+        <v>119606057</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6936,25 +6936,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406239</v>
+        <v>406112</v>
       </c>
       <c r="R61" t="n">
-        <v>6853060</v>
+        <v>6852975</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119607416</v>
+        <v>119605981</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>86412</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8874,25 +8874,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406199</v>
+        <v>406117</v>
       </c>
       <c r="R80" t="n">
-        <v>6853071</v>
+        <v>6852963</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119605197</v>
+        <v>119607416</v>
       </c>
       <c r="B81" t="n">
-        <v>91821</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8976,25 +8976,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406125</v>
+        <v>406199</v>
       </c>
       <c r="R81" t="n">
-        <v>6853116</v>
+        <v>6853071</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9066,10 +9066,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119605981</v>
+        <v>119605197</v>
       </c>
       <c r="B82" t="n">
-        <v>86412</v>
+        <v>91821</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9078,25 +9078,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3690</v>
+        <v>6055</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9106,10 +9106,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406117</v>
+        <v>406125</v>
       </c>
       <c r="R82" t="n">
-        <v>6852963</v>
+        <v>6853116</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 10553-2024 artfynd.xlsx
+++ b/artfynd/A 10553-2024 artfynd.xlsx
@@ -3864,10 +3864,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119594384</v>
+        <v>119605409</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>405789</v>
+        <v>406122</v>
       </c>
       <c r="R31" t="n">
-        <v>6853218</v>
+        <v>6853010</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119605409</v>
+        <v>119607381</v>
       </c>
       <c r="B32" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3978,25 +3978,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406122</v>
+        <v>406210</v>
       </c>
       <c r="R32" t="n">
-        <v>6853010</v>
+        <v>6853084</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119607381</v>
+        <v>119594384</v>
       </c>
       <c r="B33" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406210</v>
+        <v>405789</v>
       </c>
       <c r="R33" t="n">
-        <v>6853084</v>
+        <v>6853218</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119606613</v>
+        <v>119594962</v>
       </c>
       <c r="B70" t="n">
         <v>79144</v>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406302</v>
+        <v>405828</v>
       </c>
       <c r="R70" t="n">
-        <v>6852902</v>
+        <v>6853211</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7944,10 +7944,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119607299</v>
+        <v>119606613</v>
       </c>
       <c r="B71" t="n">
-        <v>91886</v>
+        <v>79144</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7956,25 +7956,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>232140</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406211</v>
+        <v>406302</v>
       </c>
       <c r="R71" t="n">
-        <v>6853043</v>
+        <v>6852902</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8046,10 +8046,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119594962</v>
+        <v>119593289</v>
       </c>
       <c r="B72" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8058,25 +8058,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>405828</v>
+        <v>405882</v>
       </c>
       <c r="R72" t="n">
-        <v>6853211</v>
+        <v>6853270</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8148,7 +8148,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119593289</v>
+        <v>119605339</v>
       </c>
       <c r="B73" t="n">
         <v>91840</v>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>405882</v>
+        <v>406142</v>
       </c>
       <c r="R73" t="n">
-        <v>6853270</v>
+        <v>6853013</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8250,10 +8250,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119605339</v>
+        <v>119607299</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>91886</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8262,25 +8262,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8290,10 +8290,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406142</v>
+        <v>406211</v>
       </c>
       <c r="R74" t="n">
-        <v>6853013</v>
+        <v>6853043</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119605981</v>
+        <v>119607416</v>
       </c>
       <c r="B80" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8874,25 +8874,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406117</v>
+        <v>406199</v>
       </c>
       <c r="R80" t="n">
-        <v>6852963</v>
+        <v>6853071</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119607416</v>
+        <v>119605197</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>91821</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8976,25 +8976,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406199</v>
+        <v>406125</v>
       </c>
       <c r="R81" t="n">
-        <v>6853071</v>
+        <v>6853116</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9066,10 +9066,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119605197</v>
+        <v>119605981</v>
       </c>
       <c r="B82" t="n">
-        <v>91821</v>
+        <v>86412</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9078,25 +9078,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6055</v>
+        <v>3690</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9106,10 +9106,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406125</v>
+        <v>406117</v>
       </c>
       <c r="R82" t="n">
-        <v>6853116</v>
+        <v>6852963</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 10553-2024 artfynd.xlsx
+++ b/artfynd/A 10553-2024 artfynd.xlsx
@@ -3150,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119589990</v>
+        <v>119589809</v>
       </c>
       <c r="B24" t="n">
-        <v>86412</v>
+        <v>78262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405898</v>
+        <v>405901</v>
       </c>
       <c r="R24" t="n">
-        <v>6853258</v>
+        <v>6853284</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119589977</v>
+        <v>119590145</v>
       </c>
       <c r="B25" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3264,25 +3264,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405905</v>
+        <v>405871</v>
       </c>
       <c r="R25" t="n">
-        <v>6853261</v>
+        <v>6853272</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119590145</v>
+        <v>119589977</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405871</v>
+        <v>405905</v>
       </c>
       <c r="R26" t="n">
-        <v>6853272</v>
+        <v>6853261</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119589809</v>
+        <v>119589990</v>
       </c>
       <c r="B28" t="n">
-        <v>78262</v>
+        <v>86412</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>405901</v>
+        <v>405898</v>
       </c>
       <c r="R28" t="n">
-        <v>6853284</v>
+        <v>6853258</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119605581</v>
+        <v>119605981</v>
       </c>
       <c r="B29" t="n">
-        <v>91844</v>
+        <v>86412</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4365</v>
+        <v>3690</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406095</v>
+        <v>406117</v>
       </c>
       <c r="R29" t="n">
-        <v>6853015</v>
+        <v>6852963</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119594040</v>
+        <v>119604965</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>405748</v>
+        <v>406086</v>
       </c>
       <c r="R30" t="n">
-        <v>6853237</v>
+        <v>6853174</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119605409</v>
+        <v>119605803</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3876,25 +3876,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406122</v>
+        <v>406080</v>
       </c>
       <c r="R31" t="n">
-        <v>6853010</v>
+        <v>6852969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119607381</v>
+        <v>119594838</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>79115</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406210</v>
+        <v>405826</v>
       </c>
       <c r="R32" t="n">
-        <v>6853084</v>
+        <v>6853257</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119594384</v>
+        <v>119594040</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405789</v>
+        <v>405748</v>
       </c>
       <c r="R33" t="n">
-        <v>6853218</v>
+        <v>6853237</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119606224</v>
+        <v>119606556</v>
       </c>
       <c r="B34" t="n">
         <v>79144</v>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406239</v>
+        <v>406315</v>
       </c>
       <c r="R34" t="n">
-        <v>6852940</v>
+        <v>6852938</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119606242</v>
+        <v>119606967</v>
       </c>
       <c r="B35" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406252</v>
+        <v>406333</v>
       </c>
       <c r="R35" t="n">
-        <v>6852922</v>
+        <v>6852963</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119595104</v>
+        <v>119596070</v>
       </c>
       <c r="B36" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405850</v>
+        <v>406104</v>
       </c>
       <c r="R36" t="n">
-        <v>6853227</v>
+        <v>6853128</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119605363</v>
+        <v>119595104</v>
       </c>
       <c r="B37" t="n">
-        <v>91834</v>
+        <v>79144</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406142</v>
+        <v>405850</v>
       </c>
       <c r="R37" t="n">
-        <v>6853013</v>
+        <v>6853227</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119607039</v>
+        <v>119606595</v>
       </c>
       <c r="B38" t="n">
-        <v>91884</v>
+        <v>90712</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406330</v>
+        <v>406313</v>
       </c>
       <c r="R38" t="n">
-        <v>6852958</v>
+        <v>6852914</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119606595</v>
+        <v>119606242</v>
       </c>
       <c r="B39" t="n">
-        <v>90712</v>
+        <v>91834</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4692,25 +4692,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406313</v>
+        <v>406252</v>
       </c>
       <c r="R39" t="n">
-        <v>6852914</v>
+        <v>6852922</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119605452</v>
+        <v>119593987</v>
       </c>
       <c r="B40" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406109</v>
+        <v>405781</v>
       </c>
       <c r="R40" t="n">
-        <v>6853016</v>
+        <v>6853291</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119596070</v>
+        <v>119595814</v>
       </c>
       <c r="B41" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406104</v>
+        <v>406037</v>
       </c>
       <c r="R41" t="n">
-        <v>6853128</v>
+        <v>6853061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4986,7 +4986,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119595814</v>
+        <v>119594509</v>
       </c>
       <c r="B42" t="n">
         <v>91834</v>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406037</v>
+        <v>405756</v>
       </c>
       <c r="R42" t="n">
-        <v>6853061</v>
+        <v>6853196</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119595947</v>
+        <v>119607021</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>86412</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5100,25 +5100,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406107</v>
+        <v>406337</v>
       </c>
       <c r="R43" t="n">
-        <v>6853091</v>
+        <v>6852957</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119594626</v>
+        <v>119593289</v>
       </c>
       <c r="B44" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5202,25 +5202,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>405772</v>
+        <v>405882</v>
       </c>
       <c r="R44" t="n">
-        <v>6853188</v>
+        <v>6853270</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119595859</v>
+        <v>119607083</v>
       </c>
       <c r="B45" t="n">
         <v>91840</v>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406074</v>
+        <v>406318</v>
       </c>
       <c r="R45" t="n">
-        <v>6853054</v>
+        <v>6852951</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119606156</v>
+        <v>119594626</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5406,25 +5406,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406215</v>
+        <v>405772</v>
       </c>
       <c r="R46" t="n">
-        <v>6852916</v>
+        <v>6853188</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119605983</v>
+        <v>119607299</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>91886</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5508,25 +5508,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406117</v>
+        <v>406211</v>
       </c>
       <c r="R47" t="n">
-        <v>6852963</v>
+        <v>6853043</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119606195</v>
+        <v>119596085</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5610,25 +5610,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406196</v>
+        <v>406101</v>
       </c>
       <c r="R48" t="n">
-        <v>6852889</v>
+        <v>6853139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5700,10 +5700,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119607098</v>
+        <v>119595459</v>
       </c>
       <c r="B49" t="n">
-        <v>77910</v>
+        <v>91834</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5716,21 +5716,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406307</v>
+        <v>405856</v>
       </c>
       <c r="R49" t="n">
-        <v>6852966</v>
+        <v>6853158</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5802,10 +5802,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119594095</v>
+        <v>119606057</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5814,25 +5814,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>405783</v>
+        <v>406112</v>
       </c>
       <c r="R50" t="n">
-        <v>6853226</v>
+        <v>6852975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119604965</v>
+        <v>119606345</v>
       </c>
       <c r="B51" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5916,25 +5916,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406086</v>
+        <v>406298</v>
       </c>
       <c r="R51" t="n">
-        <v>6853174</v>
+        <v>6852920</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6006,7 +6006,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119606560</v>
+        <v>119595947</v>
       </c>
       <c r="B52" t="n">
         <v>91840</v>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406316</v>
+        <v>406107</v>
       </c>
       <c r="R52" t="n">
-        <v>6852927</v>
+        <v>6853091</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119606304</v>
+        <v>119606888</v>
       </c>
       <c r="B53" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6124,21 +6124,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406281</v>
+        <v>406348</v>
       </c>
       <c r="R53" t="n">
-        <v>6852896</v>
+        <v>6852954</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,10 +6210,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119605062</v>
+        <v>119605202</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6222,25 +6222,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406129</v>
+        <v>406125</v>
       </c>
       <c r="R54" t="n">
-        <v>6853142</v>
+        <v>6853116</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119595839</v>
+        <v>119607138</v>
       </c>
       <c r="B55" t="n">
         <v>91840</v>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406032</v>
+        <v>406299</v>
       </c>
       <c r="R55" t="n">
-        <v>6853036</v>
+        <v>6852956</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119606556</v>
+        <v>119606195</v>
       </c>
       <c r="B56" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6426,25 +6426,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406315</v>
+        <v>406196</v>
       </c>
       <c r="R56" t="n">
-        <v>6852938</v>
+        <v>6852889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6516,10 +6516,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119594509</v>
+        <v>119594384</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6528,25 +6528,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>405756</v>
+        <v>405789</v>
       </c>
       <c r="R57" t="n">
-        <v>6853196</v>
+        <v>6853218</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119595459</v>
+        <v>119606304</v>
       </c>
       <c r="B58" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6630,25 +6630,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>405856</v>
+        <v>406281</v>
       </c>
       <c r="R58" t="n">
-        <v>6853158</v>
+        <v>6852896</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6720,10 +6720,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119594067</v>
+        <v>119606560</v>
       </c>
       <c r="B59" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6732,25 +6732,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>405762</v>
+        <v>406316</v>
       </c>
       <c r="R59" t="n">
-        <v>6853240</v>
+        <v>6852927</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119607335</v>
+        <v>119607381</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6834,25 +6834,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406239</v>
+        <v>406210</v>
       </c>
       <c r="R60" t="n">
-        <v>6853060</v>
+        <v>6853084</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119606057</v>
+        <v>119605363</v>
       </c>
       <c r="B61" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406112</v>
+        <v>406142</v>
       </c>
       <c r="R61" t="n">
-        <v>6852975</v>
+        <v>6853013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119607190</v>
+        <v>119607416</v>
       </c>
       <c r="B62" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7038,25 +7038,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406222</v>
+        <v>406199</v>
       </c>
       <c r="R62" t="n">
-        <v>6853034</v>
+        <v>6853071</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7128,10 +7128,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119606888</v>
+        <v>119607098</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>77910</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7140,25 +7140,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406348</v>
+        <v>406307</v>
       </c>
       <c r="R63" t="n">
-        <v>6852954</v>
+        <v>6852966</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7230,10 +7230,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119607611</v>
+        <v>119595859</v>
       </c>
       <c r="B64" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7246,21 +7246,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406167</v>
+        <v>406074</v>
       </c>
       <c r="R64" t="n">
-        <v>6853139</v>
+        <v>6853054</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7332,10 +7332,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119605803</v>
+        <v>119605983</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7344,25 +7344,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406080</v>
+        <v>406117</v>
       </c>
       <c r="R65" t="n">
-        <v>6852969</v>
+        <v>6852963</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119594838</v>
+        <v>119605345</v>
       </c>
       <c r="B66" t="n">
-        <v>79115</v>
+        <v>91832</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7450,21 +7450,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>4361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>405826</v>
+        <v>406142</v>
       </c>
       <c r="R66" t="n">
-        <v>6853257</v>
+        <v>6853013</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119606967</v>
+        <v>119605581</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7548,25 +7548,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406333</v>
+        <v>406095</v>
       </c>
       <c r="R67" t="n">
-        <v>6852963</v>
+        <v>6853015</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119607365</v>
+        <v>119595382</v>
       </c>
       <c r="B68" t="n">
-        <v>91884</v>
+        <v>89252</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7650,25 +7650,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7678,10 +7678,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406230</v>
+        <v>405834</v>
       </c>
       <c r="R68" t="n">
-        <v>6853085</v>
+        <v>6853151</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7740,10 +7740,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119607021</v>
+        <v>119594067</v>
       </c>
       <c r="B69" t="n">
-        <v>86412</v>
+        <v>79115</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7756,21 +7756,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3690</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406337</v>
+        <v>405762</v>
       </c>
       <c r="R69" t="n">
-        <v>6852957</v>
+        <v>6853240</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119594962</v>
+        <v>119605062</v>
       </c>
       <c r="B70" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7854,25 +7854,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>405828</v>
+        <v>406129</v>
       </c>
       <c r="R70" t="n">
-        <v>6853211</v>
+        <v>6853142</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7944,10 +7944,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119606613</v>
+        <v>119607611</v>
       </c>
       <c r="B71" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7956,25 +7956,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406302</v>
+        <v>406167</v>
       </c>
       <c r="R71" t="n">
-        <v>6852902</v>
+        <v>6853139</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8046,10 +8046,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119593289</v>
+        <v>119594862</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8058,25 +8058,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>405882</v>
+        <v>405853</v>
       </c>
       <c r="R72" t="n">
-        <v>6853270</v>
+        <v>6853232</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8250,10 +8250,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119607299</v>
+        <v>119606156</v>
       </c>
       <c r="B74" t="n">
-        <v>91886</v>
+        <v>91840</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8262,25 +8262,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8290,10 +8290,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406211</v>
+        <v>406215</v>
       </c>
       <c r="R74" t="n">
-        <v>6853043</v>
+        <v>6852916</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8352,10 +8352,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119605202</v>
+        <v>119605409</v>
       </c>
       <c r="B75" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8364,25 +8364,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406125</v>
+        <v>406122</v>
       </c>
       <c r="R75" t="n">
-        <v>6853116</v>
+        <v>6853010</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8454,10 +8454,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119605345</v>
+        <v>119595702</v>
       </c>
       <c r="B76" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8470,21 +8470,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406142</v>
+        <v>406051</v>
       </c>
       <c r="R76" t="n">
-        <v>6853013</v>
+        <v>6853072</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8556,10 +8556,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119596085</v>
+        <v>119606224</v>
       </c>
       <c r="B77" t="n">
-        <v>91883</v>
+        <v>79144</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8572,21 +8572,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406101</v>
+        <v>406239</v>
       </c>
       <c r="R77" t="n">
-        <v>6853139</v>
+        <v>6852940</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8658,10 +8658,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119595382</v>
+        <v>119605452</v>
       </c>
       <c r="B78" t="n">
-        <v>89252</v>
+        <v>86412</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8670,25 +8670,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6276</v>
+        <v>3690</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>405834</v>
+        <v>406109</v>
       </c>
       <c r="R78" t="n">
-        <v>6853151</v>
+        <v>6853016</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8760,10 +8760,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119594862</v>
+        <v>119607365</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8776,21 +8776,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>405853</v>
+        <v>406230</v>
       </c>
       <c r="R79" t="n">
-        <v>6853232</v>
+        <v>6853085</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119607416</v>
+        <v>119606613</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8874,25 +8874,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406199</v>
+        <v>406302</v>
       </c>
       <c r="R80" t="n">
-        <v>6853071</v>
+        <v>6852902</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119605197</v>
+        <v>119605966</v>
       </c>
       <c r="B81" t="n">
-        <v>91821</v>
+        <v>79144</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8976,25 +8976,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6055</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406125</v>
+        <v>406126</v>
       </c>
       <c r="R81" t="n">
-        <v>6853116</v>
+        <v>6852920</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9066,10 +9066,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119605981</v>
+        <v>119594962</v>
       </c>
       <c r="B82" t="n">
-        <v>86412</v>
+        <v>79144</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9082,21 +9082,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9106,10 +9106,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>406117</v>
+        <v>405828</v>
       </c>
       <c r="R82" t="n">
-        <v>6852963</v>
+        <v>6853211</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9168,7 +9168,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119607138</v>
+        <v>119607335</v>
       </c>
       <c r="B83" t="n">
         <v>91840</v>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406299</v>
+        <v>406239</v>
       </c>
       <c r="R83" t="n">
-        <v>6852956</v>
+        <v>6853060</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9270,10 +9270,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119606345</v>
+        <v>119594187</v>
       </c>
       <c r="B84" t="n">
-        <v>91852</v>
+        <v>78171</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9282,25 +9282,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406298</v>
+        <v>405785</v>
       </c>
       <c r="R84" t="n">
-        <v>6852920</v>
+        <v>6853239</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9372,7 +9372,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119607083</v>
+        <v>119594095</v>
       </c>
       <c r="B85" t="n">
         <v>91840</v>
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406318</v>
+        <v>405783</v>
       </c>
       <c r="R85" t="n">
-        <v>6852951</v>
+        <v>6853226</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9474,10 +9474,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119593987</v>
+        <v>119607190</v>
       </c>
       <c r="B86" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9486,25 +9486,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>405781</v>
+        <v>406222</v>
       </c>
       <c r="R86" t="n">
-        <v>6853291</v>
+        <v>6853034</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9576,10 +9576,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119605966</v>
+        <v>119595839</v>
       </c>
       <c r="B87" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9588,25 +9588,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406126</v>
+        <v>406032</v>
       </c>
       <c r="R87" t="n">
-        <v>6852920</v>
+        <v>6853036</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9678,10 +9678,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119594187</v>
+        <v>119605197</v>
       </c>
       <c r="B88" t="n">
-        <v>78171</v>
+        <v>91821</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9690,25 +9690,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6055</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9718,10 +9718,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>405785</v>
+        <v>406125</v>
       </c>
       <c r="R88" t="n">
-        <v>6853239</v>
+        <v>6853116</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9780,7 +9780,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119595702</v>
+        <v>119607039</v>
       </c>
       <c r="B89" t="n">
         <v>91884</v>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406051</v>
+        <v>406330</v>
       </c>
       <c r="R89" t="n">
-        <v>6853072</v>
+        <v>6852958</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 10553-2024 artfynd.xlsx
+++ b/artfynd/A 10553-2024 artfynd.xlsx
@@ -6618,10 +6618,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119606304</v>
+        <v>119606560</v>
       </c>
       <c r="B58" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6634,21 +6634,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406281</v>
+        <v>406316</v>
       </c>
       <c r="R58" t="n">
-        <v>6852896</v>
+        <v>6852927</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6720,10 +6720,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119606560</v>
+        <v>119607381</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6732,25 +6732,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406316</v>
+        <v>406210</v>
       </c>
       <c r="R59" t="n">
-        <v>6852927</v>
+        <v>6853084</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119607381</v>
+        <v>119606304</v>
       </c>
       <c r="B60" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6834,25 +6834,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406210</v>
+        <v>406281</v>
       </c>
       <c r="R60" t="n">
-        <v>6853084</v>
+        <v>6852896</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119605345</v>
+        <v>119605581</v>
       </c>
       <c r="B66" t="n">
-        <v>91832</v>
+        <v>91844</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7446,25 +7446,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406142</v>
+        <v>406095</v>
       </c>
       <c r="R66" t="n">
-        <v>6853013</v>
+        <v>6853015</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119605581</v>
+        <v>119605345</v>
       </c>
       <c r="B67" t="n">
-        <v>91844</v>
+        <v>91832</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7548,25 +7548,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406095</v>
+        <v>406142</v>
       </c>
       <c r="R67" t="n">
-        <v>6853015</v>
+        <v>6853013</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8352,10 +8352,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119605409</v>
+        <v>119606224</v>
       </c>
       <c r="B75" t="n">
-        <v>91852</v>
+        <v>79144</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8364,25 +8364,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406122</v>
+        <v>406239</v>
       </c>
       <c r="R75" t="n">
-        <v>6853010</v>
+        <v>6852940</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8454,10 +8454,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119595702</v>
+        <v>119605409</v>
       </c>
       <c r="B76" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8466,25 +8466,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406051</v>
+        <v>406122</v>
       </c>
       <c r="R76" t="n">
-        <v>6853072</v>
+        <v>6853010</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8556,10 +8556,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119606224</v>
+        <v>119595702</v>
       </c>
       <c r="B77" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8572,21 +8572,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406239</v>
+        <v>406051</v>
       </c>
       <c r="R77" t="n">
-        <v>6852940</v>
+        <v>6853072</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9066,10 +9066,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119594962</v>
+        <v>119594187</v>
       </c>
       <c r="B82" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9082,21 +9082,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9106,10 +9106,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>405828</v>
+        <v>405785</v>
       </c>
       <c r="R82" t="n">
-        <v>6853211</v>
+        <v>6853239</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9270,10 +9270,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119594187</v>
+        <v>119594962</v>
       </c>
       <c r="B84" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9286,21 +9286,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>405785</v>
+        <v>405828</v>
       </c>
       <c r="R84" t="n">
-        <v>6853239</v>
+        <v>6853211</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9372,10 +9372,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119594095</v>
+        <v>119607190</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9384,25 +9384,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>405783</v>
+        <v>406222</v>
       </c>
       <c r="R85" t="n">
-        <v>6853226</v>
+        <v>6853034</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9474,10 +9474,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119607190</v>
+        <v>119594095</v>
       </c>
       <c r="B86" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9486,25 +9486,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406222</v>
+        <v>405783</v>
       </c>
       <c r="R86" t="n">
-        <v>6853034</v>
+        <v>6853226</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 10553-2024 artfynd.xlsx
+++ b/artfynd/A 10553-2024 artfynd.xlsx
@@ -3048,10 +3048,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119590109</v>
+        <v>119589809</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3060,25 +3060,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405881</v>
+        <v>405901</v>
       </c>
       <c r="R23" t="n">
-        <v>6853285</v>
+        <v>6853284</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119589809</v>
+        <v>119590258</v>
       </c>
       <c r="B24" t="n">
-        <v>78262</v>
+        <v>91852</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,25 +3162,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405901</v>
+        <v>405841</v>
       </c>
       <c r="R24" t="n">
-        <v>6853284</v>
+        <v>6853246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119590145</v>
+        <v>119589990</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>86412</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3264,25 +3264,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405871</v>
+        <v>405898</v>
       </c>
       <c r="R25" t="n">
-        <v>6853272</v>
+        <v>6853258</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119590258</v>
+        <v>119590145</v>
       </c>
       <c r="B27" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>405841</v>
+        <v>405871</v>
       </c>
       <c r="R27" t="n">
-        <v>6853246</v>
+        <v>6853272</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119589990</v>
+        <v>119590109</v>
       </c>
       <c r="B28" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3570,25 +3570,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>405898</v>
+        <v>405881</v>
       </c>
       <c r="R28" t="n">
-        <v>6853258</v>
+        <v>6853285</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119605981</v>
+        <v>119607098</v>
       </c>
       <c r="B29" t="n">
-        <v>86412</v>
+        <v>77910</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3690</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406117</v>
+        <v>406307</v>
       </c>
       <c r="R29" t="n">
-        <v>6852963</v>
+        <v>6852966</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119604965</v>
+        <v>119607299</v>
       </c>
       <c r="B30" t="n">
-        <v>91834</v>
+        <v>91886</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>232140</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406086</v>
+        <v>406211</v>
       </c>
       <c r="R30" t="n">
-        <v>6853174</v>
+        <v>6853043</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119605803</v>
+        <v>119593289</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3876,25 +3876,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406080</v>
+        <v>405882</v>
       </c>
       <c r="R31" t="n">
-        <v>6852969</v>
+        <v>6853270</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119594838</v>
+        <v>119605983</v>
       </c>
       <c r="B32" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3978,25 +3978,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405826</v>
+        <v>406117</v>
       </c>
       <c r="R32" t="n">
-        <v>6853257</v>
+        <v>6852963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119594040</v>
+        <v>119594962</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405748</v>
+        <v>405828</v>
       </c>
       <c r="R33" t="n">
-        <v>6853237</v>
+        <v>6853211</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119606556</v>
+        <v>119605202</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4186,21 +4186,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406315</v>
+        <v>406125</v>
       </c>
       <c r="R34" t="n">
-        <v>6852938</v>
+        <v>6853116</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119606967</v>
+        <v>119606156</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406333</v>
+        <v>406215</v>
       </c>
       <c r="R35" t="n">
-        <v>6852963</v>
+        <v>6852916</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119596070</v>
+        <v>119605345</v>
       </c>
       <c r="B36" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406104</v>
+        <v>406142</v>
       </c>
       <c r="R36" t="n">
-        <v>6853128</v>
+        <v>6853013</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119595104</v>
+        <v>119607611</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,25 +4488,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>405850</v>
+        <v>406167</v>
       </c>
       <c r="R37" t="n">
-        <v>6853227</v>
+        <v>6853139</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119606595</v>
+        <v>119607039</v>
       </c>
       <c r="B38" t="n">
-        <v>90712</v>
+        <v>91884</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406313</v>
+        <v>406330</v>
       </c>
       <c r="R38" t="n">
-        <v>6852914</v>
+        <v>6852958</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119606242</v>
+        <v>119607381</v>
       </c>
       <c r="B39" t="n">
         <v>91834</v>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406252</v>
+        <v>406210</v>
       </c>
       <c r="R39" t="n">
-        <v>6852922</v>
+        <v>6853084</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119593987</v>
+        <v>119606613</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>405781</v>
+        <v>406302</v>
       </c>
       <c r="R40" t="n">
-        <v>6853291</v>
+        <v>6852902</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119595814</v>
+        <v>119595104</v>
       </c>
       <c r="B41" t="n">
-        <v>91834</v>
+        <v>79144</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406037</v>
+        <v>405850</v>
       </c>
       <c r="R41" t="n">
-        <v>6853061</v>
+        <v>6853227</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4986,10 +4986,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119594509</v>
+        <v>119606560</v>
       </c>
       <c r="B42" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>405756</v>
+        <v>406316</v>
       </c>
       <c r="R42" t="n">
-        <v>6853196</v>
+        <v>6852927</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119607021</v>
+        <v>119604965</v>
       </c>
       <c r="B43" t="n">
-        <v>86412</v>
+        <v>91834</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406337</v>
+        <v>406086</v>
       </c>
       <c r="R43" t="n">
-        <v>6852957</v>
+        <v>6853174</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119593289</v>
+        <v>119595382</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5202,25 +5202,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>405882</v>
+        <v>405834</v>
       </c>
       <c r="R44" t="n">
-        <v>6853270</v>
+        <v>6853151</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119607083</v>
+        <v>119605981</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>86412</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,25 +5304,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406318</v>
+        <v>406117</v>
       </c>
       <c r="R45" t="n">
-        <v>6852951</v>
+        <v>6852963</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119594626</v>
+        <v>119605197</v>
       </c>
       <c r="B46" t="n">
-        <v>91844</v>
+        <v>91821</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5410,21 +5410,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4365</v>
+        <v>6055</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>405772</v>
+        <v>406125</v>
       </c>
       <c r="R46" t="n">
-        <v>6853188</v>
+        <v>6853116</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119607299</v>
+        <v>119605966</v>
       </c>
       <c r="B47" t="n">
-        <v>91886</v>
+        <v>79144</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5508,25 +5508,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>232140</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406211</v>
+        <v>406126</v>
       </c>
       <c r="R47" t="n">
-        <v>6853043</v>
+        <v>6852920</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119596085</v>
+        <v>119594862</v>
       </c>
       <c r="B48" t="n">
-        <v>91883</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5614,21 +5614,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5448</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406101</v>
+        <v>405853</v>
       </c>
       <c r="R48" t="n">
-        <v>6853139</v>
+        <v>6853232</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5700,10 +5700,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119595459</v>
+        <v>119605581</v>
       </c>
       <c r="B49" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5712,25 +5712,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>405856</v>
+        <v>406095</v>
       </c>
       <c r="R49" t="n">
-        <v>6853158</v>
+        <v>6853015</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5802,10 +5802,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119606057</v>
+        <v>119607083</v>
       </c>
       <c r="B50" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5814,25 +5814,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406112</v>
+        <v>406318</v>
       </c>
       <c r="R50" t="n">
-        <v>6852975</v>
+        <v>6852951</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119606345</v>
+        <v>119605803</v>
       </c>
       <c r="B51" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5916,25 +5916,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406298</v>
+        <v>406080</v>
       </c>
       <c r="R51" t="n">
-        <v>6852920</v>
+        <v>6852969</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6006,7 +6006,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119595947</v>
+        <v>119593987</v>
       </c>
       <c r="B52" t="n">
         <v>91840</v>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406107</v>
+        <v>405781</v>
       </c>
       <c r="R52" t="n">
-        <v>6853091</v>
+        <v>6853291</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119606888</v>
+        <v>119607138</v>
       </c>
       <c r="B53" t="n">
         <v>91840</v>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406348</v>
+        <v>406299</v>
       </c>
       <c r="R53" t="n">
-        <v>6852954</v>
+        <v>6852956</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,10 +6210,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119605202</v>
+        <v>119606888</v>
       </c>
       <c r="B54" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6222,25 +6222,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406125</v>
+        <v>406348</v>
       </c>
       <c r="R54" t="n">
-        <v>6853116</v>
+        <v>6852954</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119607138</v>
+        <v>119594384</v>
       </c>
       <c r="B55" t="n">
         <v>91840</v>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406299</v>
+        <v>405789</v>
       </c>
       <c r="R55" t="n">
-        <v>6852956</v>
+        <v>6853218</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6414,7 +6414,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119606195</v>
+        <v>119594095</v>
       </c>
       <c r="B56" t="n">
         <v>91840</v>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406196</v>
+        <v>405783</v>
       </c>
       <c r="R56" t="n">
-        <v>6852889</v>
+        <v>6853226</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6516,10 +6516,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119594384</v>
+        <v>119605363</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6528,25 +6528,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>405789</v>
+        <v>406142</v>
       </c>
       <c r="R57" t="n">
-        <v>6853218</v>
+        <v>6853013</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119606560</v>
+        <v>119594187</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6630,25 +6630,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406316</v>
+        <v>405785</v>
       </c>
       <c r="R58" t="n">
-        <v>6852927</v>
+        <v>6853239</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6720,10 +6720,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119607381</v>
+        <v>119606345</v>
       </c>
       <c r="B59" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6732,25 +6732,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406210</v>
+        <v>406298</v>
       </c>
       <c r="R59" t="n">
-        <v>6853084</v>
+        <v>6852920</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119606304</v>
+        <v>119605062</v>
       </c>
       <c r="B60" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6838,21 +6838,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406281</v>
+        <v>406129</v>
       </c>
       <c r="R60" t="n">
-        <v>6852896</v>
+        <v>6853142</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6924,7 +6924,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119605363</v>
+        <v>119606242</v>
       </c>
       <c r="B61" t="n">
         <v>91834</v>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406142</v>
+        <v>406252</v>
       </c>
       <c r="R61" t="n">
-        <v>6853013</v>
+        <v>6852922</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7128,10 +7128,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119607098</v>
+        <v>119606967</v>
       </c>
       <c r="B63" t="n">
-        <v>77910</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7140,25 +7140,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406307</v>
+        <v>406333</v>
       </c>
       <c r="R63" t="n">
-        <v>6852966</v>
+        <v>6852963</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7230,10 +7230,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119595859</v>
+        <v>119606224</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7242,25 +7242,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406074</v>
+        <v>406239</v>
       </c>
       <c r="R64" t="n">
-        <v>6853054</v>
+        <v>6852940</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7332,10 +7332,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119605983</v>
+        <v>119594626</v>
       </c>
       <c r="B65" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7344,25 +7344,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406117</v>
+        <v>405772</v>
       </c>
       <c r="R65" t="n">
-        <v>6852963</v>
+        <v>6853188</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119605581</v>
+        <v>119595859</v>
       </c>
       <c r="B66" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7446,25 +7446,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406095</v>
+        <v>406074</v>
       </c>
       <c r="R66" t="n">
-        <v>6853015</v>
+        <v>6853054</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119605345</v>
+        <v>119595702</v>
       </c>
       <c r="B67" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7552,21 +7552,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406142</v>
+        <v>406051</v>
       </c>
       <c r="R67" t="n">
-        <v>6853013</v>
+        <v>6853072</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119595382</v>
+        <v>119595814</v>
       </c>
       <c r="B68" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7650,25 +7650,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7678,10 +7678,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>405834</v>
+        <v>406037</v>
       </c>
       <c r="R68" t="n">
-        <v>6853151</v>
+        <v>6853061</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7740,10 +7740,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119594067</v>
+        <v>119595947</v>
       </c>
       <c r="B69" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7752,25 +7752,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>405762</v>
+        <v>406107</v>
       </c>
       <c r="R69" t="n">
-        <v>6853240</v>
+        <v>6853091</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119605062</v>
+        <v>119607190</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7854,25 +7854,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406129</v>
+        <v>406222</v>
       </c>
       <c r="R70" t="n">
-        <v>6853142</v>
+        <v>6853034</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7944,10 +7944,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119607611</v>
+        <v>119596070</v>
       </c>
       <c r="B71" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7956,25 +7956,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406167</v>
+        <v>406104</v>
       </c>
       <c r="R71" t="n">
-        <v>6853139</v>
+        <v>6853128</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8046,10 +8046,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119594862</v>
+        <v>119606195</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8058,25 +8058,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>405853</v>
+        <v>406196</v>
       </c>
       <c r="R72" t="n">
-        <v>6853232</v>
+        <v>6852889</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119605339</v>
+        <v>119606556</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8160,25 +8160,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406142</v>
+        <v>406315</v>
       </c>
       <c r="R73" t="n">
-        <v>6853013</v>
+        <v>6852938</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8250,10 +8250,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119606156</v>
+        <v>119606595</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8262,25 +8262,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8290,10 +8290,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406215</v>
+        <v>406313</v>
       </c>
       <c r="R74" t="n">
-        <v>6852916</v>
+        <v>6852914</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8352,10 +8352,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119606224</v>
+        <v>119605339</v>
       </c>
       <c r="B75" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8364,25 +8364,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406239</v>
+        <v>406142</v>
       </c>
       <c r="R75" t="n">
-        <v>6852940</v>
+        <v>6853013</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8556,10 +8556,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119595702</v>
+        <v>119607335</v>
       </c>
       <c r="B77" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8568,25 +8568,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406051</v>
+        <v>406239</v>
       </c>
       <c r="R77" t="n">
-        <v>6853072</v>
+        <v>6853060</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119607365</v>
+        <v>119606057</v>
       </c>
       <c r="B79" t="n">
         <v>91884</v>
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406230</v>
+        <v>406112</v>
       </c>
       <c r="R79" t="n">
-        <v>6853085</v>
+        <v>6852975</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119606613</v>
+        <v>119594509</v>
       </c>
       <c r="B80" t="n">
-        <v>79144</v>
+        <v>91834</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406302</v>
+        <v>405756</v>
       </c>
       <c r="R80" t="n">
-        <v>6852902</v>
+        <v>6853196</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119605966</v>
+        <v>119595839</v>
       </c>
       <c r="B81" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8976,25 +8976,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406126</v>
+        <v>406032</v>
       </c>
       <c r="R81" t="n">
-        <v>6852920</v>
+        <v>6853036</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9066,10 +9066,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119594187</v>
+        <v>119594838</v>
       </c>
       <c r="B82" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9082,21 +9082,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9106,10 +9106,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>405785</v>
+        <v>405826</v>
       </c>
       <c r="R82" t="n">
-        <v>6853239</v>
+        <v>6853257</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9168,7 +9168,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119607335</v>
+        <v>119594040</v>
       </c>
       <c r="B83" t="n">
         <v>91840</v>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>406239</v>
+        <v>405748</v>
       </c>
       <c r="R83" t="n">
-        <v>6853060</v>
+        <v>6853237</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9270,10 +9270,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119594962</v>
+        <v>119607021</v>
       </c>
       <c r="B84" t="n">
-        <v>79144</v>
+        <v>86412</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9286,21 +9286,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>405828</v>
+        <v>406337</v>
       </c>
       <c r="R84" t="n">
-        <v>6853211</v>
+        <v>6852957</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9372,10 +9372,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119607190</v>
+        <v>119595459</v>
       </c>
       <c r="B85" t="n">
-        <v>78263</v>
+        <v>91834</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9388,21 +9388,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>406222</v>
+        <v>405856</v>
       </c>
       <c r="R85" t="n">
-        <v>6853034</v>
+        <v>6853158</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9474,10 +9474,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119594095</v>
+        <v>119596085</v>
       </c>
       <c r="B86" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9486,25 +9486,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>405783</v>
+        <v>406101</v>
       </c>
       <c r="R86" t="n">
-        <v>6853226</v>
+        <v>6853139</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9576,10 +9576,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119595839</v>
+        <v>119606304</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9592,21 +9592,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406032</v>
+        <v>406281</v>
       </c>
       <c r="R87" t="n">
-        <v>6853036</v>
+        <v>6852896</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9678,10 +9678,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119605197</v>
+        <v>119607365</v>
       </c>
       <c r="B88" t="n">
-        <v>91821</v>
+        <v>91884</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9690,25 +9690,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6055</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9718,10 +9718,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406125</v>
+        <v>406230</v>
       </c>
       <c r="R88" t="n">
-        <v>6853116</v>
+        <v>6853085</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9780,10 +9780,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119607039</v>
+        <v>119594067</v>
       </c>
       <c r="B89" t="n">
-        <v>91884</v>
+        <v>79115</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406330</v>
+        <v>405762</v>
       </c>
       <c r="R89" t="n">
-        <v>6852958</v>
+        <v>6853240</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 10553-2024 artfynd.xlsx
+++ b/artfynd/A 10553-2024 artfynd.xlsx
@@ -4680,10 +4680,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119607381</v>
+        <v>119606613</v>
       </c>
       <c r="B39" t="n">
-        <v>91834</v>
+        <v>79144</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4696,21 +4696,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406210</v>
+        <v>406302</v>
       </c>
       <c r="R39" t="n">
-        <v>6853084</v>
+        <v>6852902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4782,7 +4782,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119606613</v>
+        <v>119595104</v>
       </c>
       <c r="B40" t="n">
         <v>79144</v>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406302</v>
+        <v>405850</v>
       </c>
       <c r="R40" t="n">
-        <v>6852902</v>
+        <v>6853227</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119595104</v>
+        <v>119607381</v>
       </c>
       <c r="B41" t="n">
-        <v>79144</v>
+        <v>91834</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>405850</v>
+        <v>406210</v>
       </c>
       <c r="R41" t="n">
-        <v>6853227</v>
+        <v>6853084</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119605981</v>
+        <v>119605197</v>
       </c>
       <c r="B45" t="n">
-        <v>86412</v>
+        <v>91821</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,25 +5304,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3690</v>
+        <v>6055</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406117</v>
+        <v>406125</v>
       </c>
       <c r="R45" t="n">
-        <v>6852963</v>
+        <v>6853116</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119605197</v>
+        <v>119605966</v>
       </c>
       <c r="B46" t="n">
-        <v>91821</v>
+        <v>79144</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5406,25 +5406,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6055</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406125</v>
+        <v>406126</v>
       </c>
       <c r="R46" t="n">
-        <v>6853116</v>
+        <v>6852920</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119605966</v>
+        <v>119594862</v>
       </c>
       <c r="B47" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5512,21 +5512,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406126</v>
+        <v>405853</v>
       </c>
       <c r="R47" t="n">
-        <v>6852920</v>
+        <v>6853232</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119594862</v>
+        <v>119605981</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>86412</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5614,21 +5614,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>3690</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>405853</v>
+        <v>406117</v>
       </c>
       <c r="R48" t="n">
-        <v>6853232</v>
+        <v>6852963</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119605803</v>
+        <v>119593987</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5916,25 +5916,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406080</v>
+        <v>405781</v>
       </c>
       <c r="R51" t="n">
-        <v>6852969</v>
+        <v>6853291</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119593987</v>
+        <v>119605803</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6018,25 +6018,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>405781</v>
+        <v>406080</v>
       </c>
       <c r="R52" t="n">
-        <v>6853291</v>
+        <v>6852969</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119607138</v>
+        <v>119594384</v>
       </c>
       <c r="B53" t="n">
         <v>91840</v>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406299</v>
+        <v>405789</v>
       </c>
       <c r="R53" t="n">
-        <v>6852956</v>
+        <v>6853218</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119606888</v>
+        <v>119607138</v>
       </c>
       <c r="B54" t="n">
         <v>91840</v>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406348</v>
+        <v>406299</v>
       </c>
       <c r="R54" t="n">
-        <v>6852954</v>
+        <v>6852956</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6312,7 +6312,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119594384</v>
+        <v>119606888</v>
       </c>
       <c r="B55" t="n">
         <v>91840</v>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>405789</v>
+        <v>406348</v>
       </c>
       <c r="R55" t="n">
-        <v>6853218</v>
+        <v>6852954</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6516,10 +6516,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119605363</v>
+        <v>119594187</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6532,21 +6532,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406142</v>
+        <v>405785</v>
       </c>
       <c r="R57" t="n">
-        <v>6853013</v>
+        <v>6853239</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119594187</v>
+        <v>119605363</v>
       </c>
       <c r="B58" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6634,21 +6634,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>405785</v>
+        <v>406142</v>
       </c>
       <c r="R58" t="n">
-        <v>6853239</v>
+        <v>6853013</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7944,10 +7944,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119596070</v>
+        <v>119606195</v>
       </c>
       <c r="B71" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7956,25 +7956,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406104</v>
+        <v>406196</v>
       </c>
       <c r="R71" t="n">
-        <v>6853128</v>
+        <v>6852889</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8046,10 +8046,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119606195</v>
+        <v>119596070</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8058,25 +8058,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406196</v>
+        <v>406104</v>
       </c>
       <c r="R72" t="n">
-        <v>6852889</v>
+        <v>6853128</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119606556</v>
+        <v>119606595</v>
       </c>
       <c r="B73" t="n">
-        <v>79144</v>
+        <v>90712</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8160,25 +8160,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406315</v>
+        <v>406313</v>
       </c>
       <c r="R73" t="n">
-        <v>6852938</v>
+        <v>6852914</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8250,10 +8250,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119606595</v>
+        <v>119605339</v>
       </c>
       <c r="B74" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8262,25 +8262,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8290,10 +8290,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406313</v>
+        <v>406142</v>
       </c>
       <c r="R74" t="n">
-        <v>6852914</v>
+        <v>6853013</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8352,10 +8352,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119605339</v>
+        <v>119605409</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8368,21 +8368,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406142</v>
+        <v>406122</v>
       </c>
       <c r="R75" t="n">
-        <v>6853013</v>
+        <v>6853010</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8454,10 +8454,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119605409</v>
+        <v>119607335</v>
       </c>
       <c r="B76" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8470,21 +8470,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406122</v>
+        <v>406239</v>
       </c>
       <c r="R76" t="n">
-        <v>6853010</v>
+        <v>6853060</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8556,10 +8556,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119607335</v>
+        <v>119606556</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8568,25 +8568,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406239</v>
+        <v>406315</v>
       </c>
       <c r="R77" t="n">
-        <v>6853060</v>
+        <v>6852938</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8658,10 +8658,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119605452</v>
+        <v>119606057</v>
       </c>
       <c r="B78" t="n">
-        <v>86412</v>
+        <v>91884</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8674,21 +8674,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3690</v>
+        <v>5449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406109</v>
+        <v>406112</v>
       </c>
       <c r="R78" t="n">
-        <v>6853016</v>
+        <v>6852975</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8760,10 +8760,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119606057</v>
+        <v>119605452</v>
       </c>
       <c r="B79" t="n">
-        <v>91884</v>
+        <v>86412</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8776,21 +8776,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5449</v>
+        <v>3690</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406112</v>
+        <v>406109</v>
       </c>
       <c r="R79" t="n">
-        <v>6852975</v>
+        <v>6853016</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9576,10 +9576,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119606304</v>
+        <v>119594067</v>
       </c>
       <c r="B87" t="n">
-        <v>91852</v>
+        <v>79115</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9588,25 +9588,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4366</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>406281</v>
+        <v>405762</v>
       </c>
       <c r="R87" t="n">
-        <v>6852896</v>
+        <v>6853240</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9678,10 +9678,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119607365</v>
+        <v>119606304</v>
       </c>
       <c r="B88" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9690,25 +9690,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9718,10 +9718,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406230</v>
+        <v>406281</v>
       </c>
       <c r="R88" t="n">
-        <v>6853085</v>
+        <v>6852896</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9780,10 +9780,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119594067</v>
+        <v>119607365</v>
       </c>
       <c r="B89" t="n">
-        <v>79115</v>
+        <v>91884</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>405762</v>
+        <v>406230</v>
       </c>
       <c r="R89" t="n">
-        <v>6853240</v>
+        <v>6853085</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 10553-2024 artfynd.xlsx
+++ b/artfynd/A 10553-2024 artfynd.xlsx
@@ -3048,10 +3048,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119589809</v>
+        <v>119589977</v>
       </c>
       <c r="B23" t="n">
-        <v>78262</v>
+        <v>91463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4745</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405901</v>
+        <v>405905</v>
       </c>
       <c r="R23" t="n">
-        <v>6853284</v>
+        <v>6853261</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119590258</v>
+        <v>119590145</v>
       </c>
       <c r="B24" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405841</v>
+        <v>405871</v>
       </c>
       <c r="R24" t="n">
-        <v>6853246</v>
+        <v>6853272</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119589977</v>
+        <v>119589809</v>
       </c>
       <c r="B26" t="n">
-        <v>91463</v>
+        <v>78262</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3370,21 +3370,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4745</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405905</v>
+        <v>405901</v>
       </c>
       <c r="R26" t="n">
-        <v>6853261</v>
+        <v>6853284</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119590145</v>
+        <v>119590109</v>
       </c>
       <c r="B27" t="n">
         <v>91840</v>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>405871</v>
+        <v>405881</v>
       </c>
       <c r="R27" t="n">
-        <v>6853272</v>
+        <v>6853285</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119590109</v>
+        <v>119590258</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>405881</v>
+        <v>405841</v>
       </c>
       <c r="R28" t="n">
-        <v>6853285</v>
+        <v>6853246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119607098</v>
+        <v>119607138</v>
       </c>
       <c r="B29" t="n">
-        <v>77910</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406307</v>
+        <v>406299</v>
       </c>
       <c r="R29" t="n">
-        <v>6852966</v>
+        <v>6852956</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119607299</v>
+        <v>119605983</v>
       </c>
       <c r="B30" t="n">
-        <v>91886</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406211</v>
+        <v>406117</v>
       </c>
       <c r="R30" t="n">
-        <v>6853043</v>
+        <v>6852963</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119593289</v>
+        <v>119605197</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>91821</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3876,25 +3876,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>405882</v>
+        <v>406125</v>
       </c>
       <c r="R31" t="n">
-        <v>6853270</v>
+        <v>6853116</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119605983</v>
+        <v>119595814</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3978,25 +3978,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406117</v>
+        <v>406037</v>
       </c>
       <c r="R32" t="n">
-        <v>6852963</v>
+        <v>6853061</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119594962</v>
+        <v>119605363</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>91834</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405828</v>
+        <v>406142</v>
       </c>
       <c r="R33" t="n">
-        <v>6853211</v>
+        <v>6853013</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119605202</v>
+        <v>119605803</v>
       </c>
       <c r="B34" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4186,21 +4186,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406125</v>
+        <v>406080</v>
       </c>
       <c r="R34" t="n">
-        <v>6853116</v>
+        <v>6852969</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119606156</v>
+        <v>119607335</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406215</v>
+        <v>406239</v>
       </c>
       <c r="R35" t="n">
-        <v>6852916</v>
+        <v>6853060</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119605345</v>
+        <v>119606224</v>
       </c>
       <c r="B36" t="n">
-        <v>91832</v>
+        <v>79144</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406142</v>
+        <v>406239</v>
       </c>
       <c r="R36" t="n">
-        <v>6853013</v>
+        <v>6852940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119607611</v>
+        <v>119605981</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>86412</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,25 +4488,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406167</v>
+        <v>406117</v>
       </c>
       <c r="R37" t="n">
-        <v>6853139</v>
+        <v>6852963</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119607039</v>
+        <v>119607381</v>
       </c>
       <c r="B38" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406330</v>
+        <v>406210</v>
       </c>
       <c r="R38" t="n">
-        <v>6852958</v>
+        <v>6853084</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119606613</v>
+        <v>119606304</v>
       </c>
       <c r="B39" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4692,25 +4692,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406302</v>
+        <v>406281</v>
       </c>
       <c r="R39" t="n">
-        <v>6852902</v>
+        <v>6852896</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119595104</v>
+        <v>119607190</v>
       </c>
       <c r="B40" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>405850</v>
+        <v>406222</v>
       </c>
       <c r="R40" t="n">
-        <v>6853227</v>
+        <v>6853034</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119607381</v>
+        <v>119594187</v>
       </c>
       <c r="B41" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406210</v>
+        <v>405785</v>
       </c>
       <c r="R41" t="n">
-        <v>6853084</v>
+        <v>6853239</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4986,10 +4986,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119606560</v>
+        <v>119606242</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406316</v>
+        <v>406252</v>
       </c>
       <c r="R42" t="n">
-        <v>6852927</v>
+        <v>6852922</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119604965</v>
+        <v>119605966</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>79144</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406086</v>
+        <v>406126</v>
       </c>
       <c r="R43" t="n">
-        <v>6853174</v>
+        <v>6852920</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119595382</v>
+        <v>119606556</v>
       </c>
       <c r="B44" t="n">
-        <v>89252</v>
+        <v>79144</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5202,25 +5202,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>405834</v>
+        <v>406315</v>
       </c>
       <c r="R44" t="n">
-        <v>6853151</v>
+        <v>6852938</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119605197</v>
+        <v>119594509</v>
       </c>
       <c r="B45" t="n">
-        <v>91821</v>
+        <v>91834</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,25 +5304,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406125</v>
+        <v>405756</v>
       </c>
       <c r="R45" t="n">
-        <v>6853116</v>
+        <v>6853196</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119605966</v>
+        <v>119594862</v>
       </c>
       <c r="B46" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5410,21 +5410,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406126</v>
+        <v>405853</v>
       </c>
       <c r="R46" t="n">
-        <v>6852920</v>
+        <v>6853232</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119594862</v>
+        <v>119595839</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5508,25 +5508,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>405853</v>
+        <v>406032</v>
       </c>
       <c r="R47" t="n">
-        <v>6853232</v>
+        <v>6853036</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119605981</v>
+        <v>119595702</v>
       </c>
       <c r="B48" t="n">
-        <v>86412</v>
+        <v>91884</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5614,21 +5614,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3690</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406117</v>
+        <v>406051</v>
       </c>
       <c r="R48" t="n">
-        <v>6852963</v>
+        <v>6853072</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5700,10 +5700,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119605581</v>
+        <v>119606195</v>
       </c>
       <c r="B49" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5712,25 +5712,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406095</v>
+        <v>406196</v>
       </c>
       <c r="R49" t="n">
-        <v>6853015</v>
+        <v>6852889</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5802,10 +5802,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119607083</v>
+        <v>119605345</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5814,25 +5814,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406318</v>
+        <v>406142</v>
       </c>
       <c r="R50" t="n">
-        <v>6852951</v>
+        <v>6853013</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119593987</v>
+        <v>119595947</v>
       </c>
       <c r="B51" t="n">
         <v>91840</v>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405781</v>
+        <v>406107</v>
       </c>
       <c r="R51" t="n">
-        <v>6853291</v>
+        <v>6853091</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6006,10 +6006,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119605803</v>
+        <v>119595859</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6018,25 +6018,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406080</v>
+        <v>406074</v>
       </c>
       <c r="R52" t="n">
-        <v>6852969</v>
+        <v>6853054</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119594384</v>
+        <v>119594095</v>
       </c>
       <c r="B53" t="n">
         <v>91840</v>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>405789</v>
+        <v>405783</v>
       </c>
       <c r="R53" t="n">
-        <v>6853218</v>
+        <v>6853226</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6210,7 +6210,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119607138</v>
+        <v>119607083</v>
       </c>
       <c r="B54" t="n">
         <v>91840</v>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406299</v>
+        <v>406318</v>
       </c>
       <c r="R54" t="n">
-        <v>6852956</v>
+        <v>6852951</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119606888</v>
+        <v>119606345</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406348</v>
+        <v>406298</v>
       </c>
       <c r="R55" t="n">
-        <v>6852954</v>
+        <v>6852920</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6414,7 +6414,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119594095</v>
+        <v>119606888</v>
       </c>
       <c r="B56" t="n">
         <v>91840</v>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>405783</v>
+        <v>406348</v>
       </c>
       <c r="R56" t="n">
-        <v>6853226</v>
+        <v>6852954</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6516,10 +6516,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119594187</v>
+        <v>119607611</v>
       </c>
       <c r="B57" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6528,25 +6528,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>405785</v>
+        <v>406167</v>
       </c>
       <c r="R57" t="n">
-        <v>6853239</v>
+        <v>6853139</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119605363</v>
+        <v>119594384</v>
       </c>
       <c r="B58" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6630,25 +6630,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406142</v>
+        <v>405789</v>
       </c>
       <c r="R58" t="n">
-        <v>6853013</v>
+        <v>6853218</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6720,10 +6720,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119606345</v>
+        <v>119594040</v>
       </c>
       <c r="B59" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406298</v>
+        <v>405748</v>
       </c>
       <c r="R59" t="n">
-        <v>6852920</v>
+        <v>6853237</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119605062</v>
+        <v>119607098</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>77910</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6834,25 +6834,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406129</v>
+        <v>406307</v>
       </c>
       <c r="R60" t="n">
-        <v>6853142</v>
+        <v>6852966</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119606242</v>
+        <v>119606560</v>
       </c>
       <c r="B61" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6936,25 +6936,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406252</v>
+        <v>406316</v>
       </c>
       <c r="R61" t="n">
-        <v>6852922</v>
+        <v>6852927</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119607416</v>
+        <v>119605409</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7042,21 +7042,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406199</v>
+        <v>406122</v>
       </c>
       <c r="R62" t="n">
-        <v>6853071</v>
+        <v>6853010</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7128,10 +7128,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119606967</v>
+        <v>119605581</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7140,25 +7140,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406333</v>
+        <v>406095</v>
       </c>
       <c r="R63" t="n">
-        <v>6852963</v>
+        <v>6853015</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7230,10 +7230,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119606224</v>
+        <v>119606057</v>
       </c>
       <c r="B64" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7246,21 +7246,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406239</v>
+        <v>406112</v>
       </c>
       <c r="R64" t="n">
-        <v>6852940</v>
+        <v>6852975</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7332,10 +7332,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119594626</v>
+        <v>119606967</v>
       </c>
       <c r="B65" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7344,25 +7344,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>405772</v>
+        <v>406333</v>
       </c>
       <c r="R65" t="n">
-        <v>6853188</v>
+        <v>6852963</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119595859</v>
+        <v>119595382</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7446,25 +7446,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406074</v>
+        <v>405834</v>
       </c>
       <c r="R66" t="n">
-        <v>6853054</v>
+        <v>6853151</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119595702</v>
+        <v>119594626</v>
       </c>
       <c r="B67" t="n">
-        <v>91884</v>
+        <v>91844</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7548,25 +7548,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>406051</v>
+        <v>405772</v>
       </c>
       <c r="R67" t="n">
-        <v>6853072</v>
+        <v>6853188</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119595814</v>
+        <v>119605452</v>
       </c>
       <c r="B68" t="n">
-        <v>91834</v>
+        <v>86412</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7654,21 +7654,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7678,10 +7678,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>406037</v>
+        <v>406109</v>
       </c>
       <c r="R68" t="n">
-        <v>6853061</v>
+        <v>6853016</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7740,7 +7740,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119595947</v>
+        <v>119605339</v>
       </c>
       <c r="B69" t="n">
         <v>91840</v>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>406107</v>
+        <v>406142</v>
       </c>
       <c r="R69" t="n">
-        <v>6853091</v>
+        <v>6853013</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119607190</v>
+        <v>119607039</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>91884</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7858,21 +7858,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>406222</v>
+        <v>406330</v>
       </c>
       <c r="R70" t="n">
-        <v>6853034</v>
+        <v>6852958</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7944,10 +7944,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119606195</v>
+        <v>119594838</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7956,25 +7956,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>406196</v>
+        <v>405826</v>
       </c>
       <c r="R71" t="n">
-        <v>6852889</v>
+        <v>6853257</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8046,10 +8046,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119596070</v>
+        <v>119606613</v>
       </c>
       <c r="B72" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8062,21 +8062,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>406104</v>
+        <v>406302</v>
       </c>
       <c r="R72" t="n">
-        <v>6853128</v>
+        <v>6852902</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119606595</v>
+        <v>119594962</v>
       </c>
       <c r="B73" t="n">
-        <v>90712</v>
+        <v>79144</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8160,25 +8160,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>406313</v>
+        <v>405828</v>
       </c>
       <c r="R73" t="n">
-        <v>6852914</v>
+        <v>6853211</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8250,10 +8250,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119605339</v>
+        <v>119594067</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>79115</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8262,25 +8262,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8290,10 +8290,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>406142</v>
+        <v>405762</v>
       </c>
       <c r="R74" t="n">
-        <v>6853013</v>
+        <v>6853240</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8352,10 +8352,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119605409</v>
+        <v>119596085</v>
       </c>
       <c r="B75" t="n">
-        <v>91852</v>
+        <v>91883</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8364,25 +8364,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>406122</v>
+        <v>406101</v>
       </c>
       <c r="R75" t="n">
-        <v>6853010</v>
+        <v>6853139</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8454,10 +8454,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119607335</v>
+        <v>119605202</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8466,25 +8466,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406239</v>
+        <v>406125</v>
       </c>
       <c r="R76" t="n">
-        <v>6853060</v>
+        <v>6853116</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8556,10 +8556,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119606556</v>
+        <v>119607021</v>
       </c>
       <c r="B77" t="n">
-        <v>79144</v>
+        <v>86412</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8572,21 +8572,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406315</v>
+        <v>406337</v>
       </c>
       <c r="R77" t="n">
-        <v>6852938</v>
+        <v>6852957</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8658,10 +8658,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119606057</v>
+        <v>119604965</v>
       </c>
       <c r="B78" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8674,21 +8674,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406112</v>
+        <v>406086</v>
       </c>
       <c r="R78" t="n">
-        <v>6852975</v>
+        <v>6853174</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8760,10 +8760,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119605452</v>
+        <v>119605062</v>
       </c>
       <c r="B79" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8772,25 +8772,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406109</v>
+        <v>406129</v>
       </c>
       <c r="R79" t="n">
-        <v>6853016</v>
+        <v>6853142</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119594509</v>
+        <v>119607365</v>
       </c>
       <c r="B80" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>405756</v>
+        <v>406230</v>
       </c>
       <c r="R80" t="n">
-        <v>6853196</v>
+        <v>6853085</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119595839</v>
+        <v>119595104</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8976,25 +8976,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>406032</v>
+        <v>405850</v>
       </c>
       <c r="R81" t="n">
-        <v>6853036</v>
+        <v>6853227</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9066,10 +9066,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119594838</v>
+        <v>119593289</v>
       </c>
       <c r="B82" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9078,25 +9078,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9106,10 +9106,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>405826</v>
+        <v>405882</v>
       </c>
       <c r="R82" t="n">
-        <v>6853257</v>
+        <v>6853270</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9168,10 +9168,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119594040</v>
+        <v>119595459</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9180,25 +9180,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>405748</v>
+        <v>405856</v>
       </c>
       <c r="R83" t="n">
-        <v>6853237</v>
+        <v>6853158</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9270,10 +9270,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119607021</v>
+        <v>119593987</v>
       </c>
       <c r="B84" t="n">
-        <v>86412</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9282,25 +9282,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>406337</v>
+        <v>405781</v>
       </c>
       <c r="R84" t="n">
-        <v>6852957</v>
+        <v>6853291</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9372,10 +9372,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119595459</v>
+        <v>119596070</v>
       </c>
       <c r="B85" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9388,21 +9388,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>405856</v>
+        <v>406104</v>
       </c>
       <c r="R85" t="n">
-        <v>6853158</v>
+        <v>6853128</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9474,10 +9474,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119596085</v>
+        <v>119607416</v>
       </c>
       <c r="B86" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9486,25 +9486,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>406101</v>
+        <v>406199</v>
       </c>
       <c r="R86" t="n">
-        <v>6853139</v>
+        <v>6853071</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9576,10 +9576,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119594067</v>
+        <v>119606156</v>
       </c>
       <c r="B87" t="n">
-        <v>79115</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9588,25 +9588,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>405762</v>
+        <v>406215</v>
       </c>
       <c r="R87" t="n">
-        <v>6853240</v>
+        <v>6852916</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9678,10 +9678,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119606304</v>
+        <v>119606595</v>
       </c>
       <c r="B88" t="n">
-        <v>91852</v>
+        <v>90712</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9690,25 +9690,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4366</v>
+        <v>1503</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9718,10 +9718,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>406281</v>
+        <v>406313</v>
       </c>
       <c r="R88" t="n">
-        <v>6852896</v>
+        <v>6852914</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9780,10 +9780,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119607365</v>
+        <v>119607299</v>
       </c>
       <c r="B89" t="n">
-        <v>91884</v>
+        <v>91886</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9792,25 +9792,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5449</v>
+        <v>232140</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9820,10 +9820,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>406230</v>
+        <v>406211</v>
       </c>
       <c r="R89" t="n">
-        <v>6853085</v>
+        <v>6853043</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 10553-2024 artfynd.xlsx
+++ b/artfynd/A 10553-2024 artfynd.xlsx
@@ -3966,7 +3966,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119595814</v>
+        <v>119605363</v>
       </c>
       <c r="B32" t="n">
         <v>91834</v>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406037</v>
+        <v>406142</v>
       </c>
       <c r="R32" t="n">
-        <v>6853061</v>
+        <v>6853013</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119605363</v>
+        <v>119595814</v>
       </c>
       <c r="B33" t="n">
         <v>91834</v>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406142</v>
+        <v>406037</v>
       </c>
       <c r="R33" t="n">
-        <v>6853013</v>
+        <v>6853061</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119605966</v>
+        <v>119594509</v>
       </c>
       <c r="B43" t="n">
-        <v>79144</v>
+        <v>91834</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406126</v>
+        <v>405756</v>
       </c>
       <c r="R43" t="n">
-        <v>6852920</v>
+        <v>6853196</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119606556</v>
+        <v>119605966</v>
       </c>
       <c r="B44" t="n">
         <v>79144</v>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406315</v>
+        <v>406126</v>
       </c>
       <c r="R44" t="n">
-        <v>6852938</v>
+        <v>6852920</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119594509</v>
+        <v>119606556</v>
       </c>
       <c r="B45" t="n">
-        <v>91834</v>
+        <v>79144</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>405756</v>
+        <v>406315</v>
       </c>
       <c r="R45" t="n">
-        <v>6853196</v>
+        <v>6852938</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -8454,10 +8454,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119605202</v>
+        <v>119593289</v>
       </c>
       <c r="B76" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8466,25 +8466,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>406125</v>
+        <v>405882</v>
       </c>
       <c r="R76" t="n">
-        <v>6853116</v>
+        <v>6853270</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8556,10 +8556,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119607021</v>
+        <v>119605202</v>
       </c>
       <c r="B77" t="n">
-        <v>86412</v>
+        <v>78171</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8572,21 +8572,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3690</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>406337</v>
+        <v>406125</v>
       </c>
       <c r="R77" t="n">
-        <v>6852957</v>
+        <v>6853116</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8658,10 +8658,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119604965</v>
+        <v>119607021</v>
       </c>
       <c r="B78" t="n">
-        <v>91834</v>
+        <v>86412</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8674,21 +8674,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>406086</v>
+        <v>406337</v>
       </c>
       <c r="R78" t="n">
-        <v>6853174</v>
+        <v>6852957</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8760,10 +8760,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119605062</v>
+        <v>119604965</v>
       </c>
       <c r="B79" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8772,25 +8772,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>406129</v>
+        <v>406086</v>
       </c>
       <c r="R79" t="n">
-        <v>6853142</v>
+        <v>6853174</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119607365</v>
+        <v>119605062</v>
       </c>
       <c r="B80" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8874,25 +8874,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>406230</v>
+        <v>406129</v>
       </c>
       <c r="R80" t="n">
-        <v>6853085</v>
+        <v>6853142</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119595104</v>
+        <v>119607365</v>
       </c>
       <c r="B81" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8980,21 +8980,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>405850</v>
+        <v>406230</v>
       </c>
       <c r="R81" t="n">
-        <v>6853227</v>
+        <v>6853085</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9066,10 +9066,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119593289</v>
+        <v>119595459</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9078,25 +9078,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9106,10 +9106,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>405882</v>
+        <v>405856</v>
       </c>
       <c r="R82" t="n">
-        <v>6853270</v>
+        <v>6853158</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9168,10 +9168,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119595459</v>
+        <v>119595104</v>
       </c>
       <c r="B83" t="n">
-        <v>91834</v>
+        <v>79144</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>405856</v>
+        <v>405850</v>
       </c>
       <c r="R83" t="n">
-        <v>6853158</v>
+        <v>6853227</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
